--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/04_applications_systems.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/04_applications_systems.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R0c410e9272914088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rc0a75aabb52f4228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R8e5ff8b5bcae48be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R93a68a7ff72f4c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Ra45b9fd9063f4e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R49e8f9bd50f244dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Platform Segments" sheetId="7" r:id="Rd8b140df1d784280"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Case Boundary" sheetId="8" r:id="Rdd584ec4db22464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rdfab479bf5cb4bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rae3bf1c78b334196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R6433bce67aca4a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R1a112eb0767c47ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R448e12cfdcd74948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rb46cfd486e80403a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Platform Segments" sheetId="7" r:id="R0dda73208a334f74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Case Boundary" sheetId="8" r:id="Ra4b0b17aa69b49af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -653,7 +653,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd9ed3e6a45471d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R314a20d617124f55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -844,7 +844,7 @@
         <x:v>Chief Strategy Officer / Executive Office Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P6" s="80" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Executive Office Workflow Platform (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q6" s="41" t="str">
         <x:v>High</x:v>
@@ -897,7 +897,7 @@
         <x:v>Chief Strategy Officer / Executive Office Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P7" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Executive Office Analytics Mart (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q7" s="43" t="str">
         <x:v>Medium</x:v>
@@ -950,7 +950,7 @@
         <x:v>Chief Strategy Officer / Executive Office Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P8" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Executive Office Reporting Workspace (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q8" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1003,7 +1003,7 @@
         <x:v>Retail Banking COO / FIS Core Banking Platform technology owner</x:v>
       </x:c>
       <x:c r="P9" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile FIS Core Banking Platform (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q9" s="43" t="str">
         <x:v>High</x:v>
@@ -1056,7 +1056,7 @@
         <x:v>Retail Banking COO / Branch Teller Platform technology owner</x:v>
       </x:c>
       <x:c r="P10" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Branch Teller Platform (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q10" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>Retail Banking COO / Digital Banking Servicing Portal technology owner</x:v>
       </x:c>
       <x:c r="P11" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Digital Banking Servicing Portal (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q11" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1162,7 +1162,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P12" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Commercial Lending and Treasury Workflow Platform (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q12" s="43" t="str">
         <x:v>High</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P13" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury Analytics Mart (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q13" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1268,7 +1268,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P14" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Commercial Lending and Treasury Reporting Workspace (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q14" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>Head of Cards / Cards Operations Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P15" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Operations Workflow Platform (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q15" s="43" t="str">
         <x:v>High</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>Head of Cards / Cards Operations Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P16" s="82" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Cards Operations Analytics Mart (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q16" s="45" t="str">
         <x:v>Medium</x:v>
@@ -1427,7 +1427,7 @@
         <x:v>Head of Cards / Cards Operations Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Cards Operations Reporting Workspace (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q17" t="str">
         <x:v>Medium</x:v>
@@ -1480,7 +1480,7 @@
         <x:v>Payments Leader / Payments Hub technology owner</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Payments Hub (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q18" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>Payments Leader / ACH Wire Gateway technology owner</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile ACH Wire Gateway (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q19" t="str">
         <x:v>Medium</x:v>
@@ -1586,7 +1586,7 @@
         <x:v>Payments Leader / Real-Time Payments Adapter technology owner</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Real-Time Payments Adapter (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q20" t="str">
         <x:v>Medium</x:v>
@@ -1639,7 +1639,7 @@
         <x:v>Payments Leader / Settlement Reconciliation Mart technology owner</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Settlement Reconciliation Mart (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q21" t="str">
         <x:v>Medium</x:v>
@@ -1692,7 +1692,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Consumer Lending Operations Workflow Platform (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q22" t="str">
         <x:v>High</x:v>
@@ -1745,7 +1745,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Consumer Lending Operations Analytics Mart (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q23" t="str">
         <x:v>Medium</x:v>
@@ -1798,7 +1798,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Consumer Lending Operations Reporting Workspace (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q24" t="str">
         <x:v>Medium</x:v>
@@ -1851,7 +1851,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Wealth Advisory and Brokerage Workflow Platform (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q25" t="str">
         <x:v>High</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Wealth Advisory and Brokerage Analytics Mart (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q26" t="str">
         <x:v>Medium</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage Reporting Workspace (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q27" t="str">
         <x:v>Medium</x:v>
@@ -1980,7 +1980,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Fraud Analyst Copilot: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="G28" t="str">
         <x:v>Fraud and Risk Operations core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -1995,22 +1995,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>453 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Fraud Analyst Copilot users and operations volume: Analyst case throughput and aging; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>20 interfaces or reports; 5 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: AML transaction monitoring source inventory and control-owner interview.; performance issue: model version lineage gaps.</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>Fraud Risk Operations Operational Dataset; Fraud Risk Operations Analytics Mart; Fraud Risk Operations Dashboard Inventory; Fraud Risk Operations Data Quality Rules</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Upstream: Fraud Alert Platform; downstream: Fraud Risk Operations Analytics Mart; BI/analytics consumers; Snowflake / Databricks Cloud Data Platform target where applicable</x:v>
+        <x:v>Fraud Analyst Copilot evidence path: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.. Target path: fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="O28" t="str">
         <x:v>CRO / Fraud Alert Platform technology owner</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Fraud Alert Platform (record 23) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q28" t="str">
         <x:v>High</x:v>
@@ -2033,7 +2033,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Fraud Analyst Copilot: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="G29" t="str">
         <x:v>Fraud and Risk Operations core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -2048,22 +2048,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>628 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Fraud Analyst Copilot users and operations volume: Confirmed fraud loss avoided / recovered amount baseline; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>50 interfaces or reports; 13 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Digital onboarding/KYC vendor report with identity verification and device-risk signals.; performance issue: queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>Fraud Risk Operations Operational Dataset; Fraud Risk Operations Analytics Mart; Fraud Risk Operations Dashboard Inventory; Fraud Risk Operations Data Quality Rules</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Upstream: Fraud Alert Platform; downstream: Fraud Risk Operations Analytics Mart; BI/analytics consumers; Snowflake / Databricks Cloud Data Platform target where applicable</x:v>
+        <x:v>Fraud Analyst Copilot evidence path: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.. Target path: fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>CRO / AML Transaction Monitoring technology owner</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate AML Transaction Monitoring (record 24) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q29" t="str">
         <x:v>Medium</x:v>
@@ -2086,7 +2086,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Fraud Analyst Copilot: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="G30" t="str">
         <x:v>Fraud and Risk Operations core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -2101,22 +2101,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>803 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Fraud Analyst Copilot users and operations volume: Fraud alert precision by model version; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>80 interfaces or reports; 21 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Fraud feature store design notes with feedback-loop and model governance gaps.; performance issue: case outcome feedback gaps.</x:v>
       </x:c>
       <x:c r="M30" t="str">
         <x:v>Fraud Risk Operations Operational Dataset; Fraud Risk Operations Analytics Mart; Fraud Risk Operations Dashboard Inventory; Fraud Risk Operations Data Quality Rules</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Upstream: Fraud Alert Platform; downstream: Fraud Risk Operations Analytics Mart; BI/analytics consumers; Snowflake / Databricks Cloud Data Platform target where applicable</x:v>
+        <x:v>Fraud Analyst Copilot evidence path: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.. Target path: fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="O30" t="str">
         <x:v>CRO / Fraud Case Management technology owner</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Fraud Case Management (record 25) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q30" t="str">
         <x:v>Medium</x:v>
@@ -2169,7 +2169,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Compliance and Model Risk Management Workflow Platform (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q31" t="str">
         <x:v>High</x:v>
@@ -2222,7 +2222,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management Analytics Mart (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q32" t="str">
         <x:v>Medium</x:v>
@@ -2275,7 +2275,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management Reporting Workspace (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q33" t="str">
         <x:v>Medium</x:v>
@@ -2328,7 +2328,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Contact Center and Servicing Workflow Platform (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q34" t="str">
         <x:v>High</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing Analytics Mart (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q35" t="str">
         <x:v>Medium</x:v>
@@ -2434,7 +2434,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Contact Center and Servicing Reporting Workspace (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q36" t="str">
         <x:v>Medium</x:v>
@@ -2487,7 +2487,7 @@
         <x:v>Digital Banking Product Owner / Digital Account Opening Platform technology owner</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Digital Account Opening Platform (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q37" t="str">
         <x:v>High</x:v>
@@ -2540,7 +2540,7 @@
         <x:v>Digital Banking Product Owner / KYC Identity Verification Service technology owner</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for KYC Identity Verification Service (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Medium</x:v>
@@ -2593,7 +2593,7 @@
         <x:v>Digital Banking Product Owner / Funding and Account Setup API technology owner</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Funding and Account Setup API (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Medium</x:v>
@@ -2646,7 +2646,7 @@
         <x:v>CIO / FIS Core Banking Platform technology owner</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for FIS Core Banking Platform (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>High</x:v>
@@ -2699,7 +2699,7 @@
         <x:v>CIO / IBM z/OS Core Banking Mainframe technology owner</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate IBM z/OS Core Banking Mainframe (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Medium</x:v>
@@ -2752,7 +2752,7 @@
         <x:v>CIO / Core Banking API Gateway technology owner</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Core Banking API Gateway (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Medium</x:v>
@@ -2805,7 +2805,7 @@
         <x:v>CIO / Event Streaming Integration Layer technology owner</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Event Streaming Integration Layer (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Medium</x:v>
@@ -2858,7 +2858,7 @@
         <x:v>CDAO / Customer 360 Data Product technology owner</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Customer 360 Data Product (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>High</x:v>
@@ -2911,7 +2911,7 @@
         <x:v>CDAO / CRM Customer Master technology owner</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for CRM Customer Master (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Medium</x:v>
@@ -2964,7 +2964,7 @@
         <x:v>CDAO / Identity Resolution Service technology owner</x:v>
       </x:c>
       <x:c r="P46" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Identity Resolution Service (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q46" t="str">
         <x:v>Medium</x:v>
@@ -3017,7 +3017,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P47" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Retail Banking Analytics Workflow Platform (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q47" t="str">
         <x:v>High</x:v>
@@ -3070,7 +3070,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P48" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics Analytics Mart (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q48" t="str">
         <x:v>Medium</x:v>
@@ -3123,7 +3123,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P49" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Retail Banking Analytics Reporting Workspace (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q49" t="str">
         <x:v>Medium</x:v>
@@ -3176,7 +3176,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P50" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics Workflow Platform (record 45) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q50" t="str">
         <x:v>High</x:v>
@@ -3229,7 +3229,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P51" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Cards Portfolio Analytics Analytics Mart (record 46) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q51" t="str">
         <x:v>Medium</x:v>
@@ -3282,7 +3282,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P52" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Cards Portfolio Analytics Reporting Workspace (record 47) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q52" t="str">
         <x:v>Medium</x:v>
@@ -3335,7 +3335,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P53" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Payments and Settlement Analytics Workflow Platform (record 48), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q53" t="str">
         <x:v>High</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P54" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Payments and Settlement Analytics Analytics Mart (record 49) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q54" t="str">
         <x:v>Medium</x:v>
@@ -3441,7 +3441,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P55" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments and Settlement Analytics Reporting Workspace (record 50) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q55" t="str">
         <x:v>Medium</x:v>
@@ -3464,7 +3464,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F56" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Fraud Analyst Copilot: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="G56" t="str">
         <x:v>Fraud and Risk Analytics core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -3479,22 +3479,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>380 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Fraud Analyst Copilot users and operations volume: Confirmed fraud loss avoided / recovered amount baseline; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>20 interfaces or reports; 5 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; performance issue: queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="M56" t="str">
         <x:v>Fraud Risk Analytics Operational Dataset; Fraud Risk Analytics Analytics Mart; Fraud Risk Analytics Dashboard Inventory; Fraud Risk Analytics Data Quality Rules</x:v>
       </x:c>
       <x:c r="N56" t="str">
-        <x:v>Upstream: Fraud and Risk Analytics Workflow Platform; downstream: Fraud Risk Analytics Analytics Mart; BI/analytics consumers; Snowflake / Databricks Cloud Data Platform target where applicable</x:v>
+        <x:v>Fraud Analyst Copilot evidence path: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.. Target path: fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="O56" t="str">
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P56" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Workflow Platform (record 51) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q56" t="str">
         <x:v>High</x:v>
@@ -3517,7 +3517,7 @@
         <x:v>Database / warehouse / mart</x:v>
       </x:c>
       <x:c r="F57" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Fraud Analyst Copilot: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="G57" t="str">
         <x:v>Fraud and Risk Analytics core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -3532,22 +3532,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>555 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Fraud Analyst Copilot users and operations volume: Fraud alert precision by model version; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L57" t="str">
-        <x:v>50 interfaces or reports; 13 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; performance issue: case outcome feedback gaps.</x:v>
       </x:c>
       <x:c r="M57" t="str">
         <x:v>Fraud Risk Analytics Operational Dataset; Fraud Risk Analytics Analytics Mart; Fraud Risk Analytics Dashboard Inventory; Fraud Risk Analytics Data Quality Rules</x:v>
       </x:c>
       <x:c r="N57" t="str">
-        <x:v>Upstream: Fraud and Risk Analytics Workflow Platform; downstream: Fraud Risk Analytics Analytics Mart; BI/analytics consumers; Snowflake / Databricks Cloud Data Platform target where applicable</x:v>
+        <x:v>Fraud Analyst Copilot evidence path: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.. Target path: fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="O57" t="str">
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P57" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Analytics Mart (record 52) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q57" t="str">
         <x:v>Medium</x:v>
@@ -3570,7 +3570,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F58" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Fraud Analyst Copilot: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="G58" t="str">
         <x:v>Fraud and Risk Analytics core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -3585,22 +3585,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>730 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Fraud Analyst Copilot users and operations volume: Analyst case throughput and aging; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L58" t="str">
-        <x:v>80 interfaces or reports; 21 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: AML transaction monitoring source inventory and control-owner interview.; performance issue: model version lineage gaps.</x:v>
       </x:c>
       <x:c r="M58" t="str">
         <x:v>Fraud Risk Analytics Operational Dataset; Fraud Risk Analytics Analytics Mart; Fraud Risk Analytics Dashboard Inventory; Fraud Risk Analytics Data Quality Rules</x:v>
       </x:c>
       <x:c r="N58" t="str">
-        <x:v>Upstream: Fraud and Risk Analytics Workflow Platform; downstream: Fraud Risk Analytics Analytics Mart; BI/analytics consumers; Snowflake / Databricks Cloud Data Platform target where applicable</x:v>
+        <x:v>Fraud Analyst Copilot evidence path: Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.. Target path: fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="O58" t="str">
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P58" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Reporting Workspace (record 53) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q58" t="str">
         <x:v>Medium</x:v>
@@ -3653,7 +3653,7 @@
         <x:v>CDAO / Snowflake Banking Warehouse technology owner</x:v>
       </x:c>
       <x:c r="P59" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Snowflake Banking Warehouse (record 54) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q59" t="str">
         <x:v>High</x:v>
@@ -3706,7 +3706,7 @@
         <x:v>CDAO / Databricks Risk Feature Workspace technology owner</x:v>
       </x:c>
       <x:c r="P60" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks Risk Feature Workspace (record 55) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q60" t="str">
         <x:v>Medium</x:v>
@@ -3759,7 +3759,7 @@
         <x:v>CDAO / Informatica Banking ETL technology owner</x:v>
       </x:c>
       <x:c r="P61" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Informatica Banking ETL (record 56) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q61" t="str">
         <x:v>Medium</x:v>
@@ -3812,7 +3812,7 @@
         <x:v>CDAO / Alation Data Catalog technology owner</x:v>
       </x:c>
       <x:c r="P62" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Alation Data Catalog (record 57) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q62" t="str">
         <x:v>Medium</x:v>
@@ -3865,7 +3865,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P63" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Workflow Platform (record 58), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q63" t="str">
         <x:v>High</x:v>
@@ -3918,7 +3918,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P64" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline Analytics Mart (record 59) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q64" t="str">
         <x:v>Medium</x:v>
@@ -3971,7 +3971,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P65" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline Reporting Workspace (record 60) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q65" t="str">
         <x:v>Medium</x:v>
@@ -4024,7 +4024,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P66" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Vendor and Contract Optimization Workflow Platform (record 61) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q66" t="str">
         <x:v>High</x:v>
@@ -4077,7 +4077,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P67" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Vendor and Contract Optimization Analytics Mart (record 62) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q67" t="str">
         <x:v>Medium</x:v>
@@ -4130,7 +4130,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P68" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization Reporting Workspace (record 63), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q68" t="str">
         <x:v>Medium</x:v>
@@ -4183,7 +4183,7 @@
         <x:v>CTO / ServiceNow CMDB technology owner</x:v>
       </x:c>
       <x:c r="P69" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile ServiceNow CMDB (record 64) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q69" t="str">
         <x:v>High</x:v>
@@ -4236,7 +4236,7 @@
         <x:v>CTO / IBM z/OS Mainframe Cluster technology owner</x:v>
       </x:c>
       <x:c r="P70" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IBM z/OS Mainframe Cluster (record 65) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q70" t="str">
         <x:v>Medium</x:v>
@@ -4289,7 +4289,7 @@
         <x:v>CTO / Azure Banking Landing Zone technology owner</x:v>
       </x:c>
       <x:c r="P71" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Azure Banking Landing Zone (record 66) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q71" t="str">
         <x:v>Medium</x:v>
@@ -4342,7 +4342,7 @@
         <x:v>VP IT Operations / ServiceNow ITSM technology owner</x:v>
       </x:c>
       <x:c r="P72" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm ServiceNow ITSM (record 67) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q72" t="str">
         <x:v>High</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>VP IT Operations / Splunk Observability technology owner</x:v>
       </x:c>
       <x:c r="P73" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Splunk Observability (record 68), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q73" t="str">
         <x:v>Medium</x:v>
@@ -4448,7 +4448,7 @@
         <x:v>VP IT Operations / PagerDuty Incident Response technology owner</x:v>
       </x:c>
       <x:c r="P74" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile PagerDuty Incident Response (record 69) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q74" t="str">
         <x:v>Medium</x:v>
@@ -4481,7 +4481,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f17454b62864fc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26d12e4727864ed1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4600,7 +4600,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f2ea6f9830c42a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec0e7c9129124000"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5281,7 +5281,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef92c0291f8468a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ff0e67abb514414"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5375,7 +5375,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e7752d14334205"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2730b59ae9b5477a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5485,7 +5485,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ede2262a3440a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab2eb4a5214e4aa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5615,7 +5615,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7d0d694994499a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe0d1d16ef734899"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5701,7 +5701,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra710dfa9db53401d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb77be66c71664cbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>